--- a/data/WP18/WP18_extremwerte.xlsx
+++ b/data/WP18/WP18_extremwerte.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Fraktion_Canonical</t>
   </si>
@@ -89,24 +89,6 @@
     <t xml:space="preserve">SPD</t>
   </si>
   <si>
-    <t xml:space="preserve">Dudas, Gordan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wie wirkte sich in 2018 die gegenseitige Deckungsfähigkeit von Investitions-, Sport- und Schulpauschale in Altena aus?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MHKBG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MHKBG,FM,MSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-5974.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-6111.pdf</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lüders, Nadja</t>
   </si>
   <si>
@@ -138,6 +120,21 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-8993.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wagner, Markus; Vogel, Nic Peter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immer wieder „Tumultlagen“ in Nordrhein-Westfalen: Was sind die Ursachen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IM,MKFFI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-11261.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-11647.pdf</t>
   </si>
 </sst>
 </file>
@@ -532,9 +529,11 @@
       <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="H2"/>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>159</v>
@@ -627,37 +626,37 @@
         <v>24</v>
       </c>
       <c r="B5" t="n">
-        <v>2422</v>
+        <v>6281</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>43587</v>
+        <v>44568</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>43593</v>
+        <v>44573</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
       </c>
       <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="s">
         <v>28</v>
       </c>
-      <c r="I5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>29</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -665,31 +664,31 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>6281</v>
+        <v>3478</v>
       </c>
       <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>43930</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>44568</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" s="1" t="n">
+        <v>43930</v>
+      </c>
+      <c r="G6" t="s">
         <v>32</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>44573</v>
-      </c>
-      <c r="G6" t="s">
-        <v>33</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="s">
         <v>34</v>
@@ -700,28 +699,28 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>3478</v>
+        <v>4493</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>43930</v>
+        <v>44138</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>43930</v>
+        <v>44138</v>
       </c>
       <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
         <v>38</v>
-      </c>
-      <c r="H7" t="s">
-        <v>39</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -730,10 +729,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" t="s">
         <v>40</v>
-      </c>
-      <c r="L7" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -970,13 +969,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24992FE2-BF46-476D-94A6-F2B6422E9897}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B908818F-A2AC-49B2-8C75-E490C88F4E61}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F90EB88F-AABB-4CCD-8BBC-0CE8E7315E73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D0DABC-9EAD-42B3-A9A4-65338ACE274E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4C24BCD-E4DE-4EE0-83E2-72A1F0A09819}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E85AAB3A-390C-4D7E-BB1C-6D55A4A30B2E}"/>
 </file>
--- a/data/WP18/WP18_extremwerte.xlsx
+++ b/data/WP18/WP18_extremwerte.xlsx
@@ -12,17 +12,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+  <si>
+    <t xml:space="preserve">WP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kleine_Anfrage_Nr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anfrager</t>
+  </si>
   <si>
     <t xml:space="preserve">Fraktion_Canonical</t>
   </si>
   <si>
-    <t xml:space="preserve">Kleine_Anfrage_Nr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anfrager</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anfragedatum</t>
   </si>
   <si>
@@ -50,12 +53,12 @@
     <t xml:space="preserve">Link_Drucksache_Antwort</t>
   </si>
   <si>
+    <t xml:space="preserve">Wagner, Markus</t>
+  </si>
+  <si>
     <t xml:space="preserve">AfD</t>
   </si>
   <si>
-    <t xml:space="preserve">Wagner, Markus</t>
-  </si>
-  <si>
     <t xml:space="preserve">Messerdelikte auf öffentlichen Straßen und Plätzen in Nordrhein-Westfalen im ersten Halbjahr 2025</t>
   </si>
   <si>
@@ -86,55 +89,106 @@
     <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-17897.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">Wagner, Markus; Seli-Zacharias, Enxhi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie viele Gruppenvergewaltigungen wurden im ersten Halbjahr 2025 in Nordrhein-West- falen registriert?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-15843.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-17900.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie häufig kam es im ersten Halbjahr 2025 in Nordrhein-Westfalen zu einer Vergewalti- gung auf öffentlichen Straßen oder Plätzen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-15844.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-17901.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schneider, René</t>
+  </si>
+  <si>
     <t xml:space="preserve">SPD</t>
   </si>
   <si>
-    <t xml:space="preserve">Lüders, Nadja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wieder Marketing mit der Staatskanzlei?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MBEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-16205.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-16224.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philipp, Sarah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanziert StoryMachine das Heinsbergprotokoll?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGS,FM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-8968.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-8993.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wagner, Markus; Vogel, Nic Peter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immer wieder „Tumultlagen“ in Nordrhein-Westfalen: Was sind die Ursachen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IM,MKFFI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-11261.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD17-11647.pdf</t>
+    <t xml:space="preserve">Prächtige Geschäfte mit putzigen Tieren: Wie bewertet die Landesregierung Großinves- toren in der Tiermedizin?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-17849.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-17949.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gebauer, Yvonne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transparenz beim Förderprogramm Dritte Orte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MKW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-12538.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-12706.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durdu, Tülay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schwimmen im Container: Welche Bilanz zieht die Landesregierung aus dem Modell- projekt „narwali“?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBEIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-14848.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-15060.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schalley, Zacharias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ist unser Umweltministerium noch integer?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUNV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-5020.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-5114.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baer, Alexander; Schneider, René</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warum besteuern Finanzämter in NRW die monatliche Auszahlung von Lebensversi- cherungen weiter, auch wenn der Bundesfinanzhof vor vier Jahren anders urteilte?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-12647.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.landtag.nrw.de/portal/WWW/dokumentenarchiv/Dokument/MMD18-12801.pdf</t>
   </si>
 </sst>
 </file>
@@ -506,10 +560,13 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>12</v>
+      <c r="A2" t="n">
+        <v>18</v>
       </c>
       <c r="B2" t="n">
         <v>6434</v>
@@ -517,37 +574,40 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>45919</v>
       </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>46078</v>
       </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
       <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>159</v>
-      </c>
-      <c r="K2" t="s">
-        <v>16</v>
       </c>
       <c r="L2" t="s">
         <v>17</v>
       </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>12</v>
+      <c r="A3" t="n">
+        <v>18</v>
       </c>
       <c r="B3" t="n">
         <v>6436</v>
@@ -555,37 +615,40 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>45919</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>46078</v>
       </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
       <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>159</v>
-      </c>
-      <c r="K3" t="s">
-        <v>19</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
       </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>12</v>
+      <c r="A4" t="n">
+        <v>18</v>
       </c>
       <c r="B4" t="n">
         <v>6444</v>
@@ -593,146 +656,322 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>45919</v>
       </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>46078</v>
       </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
       <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>159</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
       </c>
       <c r="L4" t="s">
         <v>23</v>
       </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>24</v>
+      <c r="A5" t="n">
+        <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>6281</v>
+        <v>6502</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>44568</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>44573</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>153</v>
+      </c>
+      <c r="L5" t="s">
         <v>27</v>
       </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>28</v>
-      </c>
-      <c r="L5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
-        <v>24</v>
+      <c r="A6" t="n">
+        <v>18</v>
       </c>
       <c r="B6" t="n">
-        <v>3478</v>
+        <v>6503</v>
       </c>
       <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>153</v>
+      </c>
+      <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>43930</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="M6" t="s">
         <v>31</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>43930</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7230</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>12</v>
       </c>
-      <c r="B7" t="n">
-        <v>4493</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="L7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>44138</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="M7" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>44138</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5004</v>
+      </c>
+      <c r="C8" t="s">
         <v>38</v>
       </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="D8" t="s">
         <v>39</v>
       </c>
-      <c r="L7" t="s">
+      <c r="E8" s="1" t="n">
+        <v>45677</v>
+      </c>
+      <c r="F8" t="s">
         <v>40</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B9" t="n">
+        <v>6114</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>45859</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11</v>
+      </c>
+      <c r="L9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2116</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>45121</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5031</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>45694</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -969,13 +1208,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B908818F-A2AC-49B2-8C75-E490C88F4E61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03A73EDF-5221-4731-A3A6-11151471F0BF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D0DABC-9EAD-42B3-A9A4-65338ACE274E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1620863E-1116-4175-BC5A-78D6E305D7ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E85AAB3A-390C-4D7E-BB1C-6D55A4A30B2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69587B9B-D2FA-47F9-87A3-94136170FEF7}"/>
 </file>
--- a/data/WP18/WP18_extremwerte.xlsx
+++ b/data/WP18/WP18_extremwerte.xlsx
@@ -1208,13 +1208,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03A73EDF-5221-4731-A3A6-11151471F0BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71C67307-94A0-4D72-942B-EEA724D37F18}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1620863E-1116-4175-BC5A-78D6E305D7ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59BCA4EC-ADC1-49EC-9C9A-3AD4A7E83988}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69587B9B-D2FA-47F9-87A3-94136170FEF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01EFBA85-1504-4138-A9FB-BC9EBDB9CC6F}"/>
 </file>